--- a/Assets/test260903/chapter0102.xlsx
+++ b/Assets/test260903/chapter0102.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="302" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B31455B6-AB2D-4FE4-AE6B-8D018193DB43}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="chapter0102" sheetId="1" r:id="rId4"/>
+    <sheet name="chapter0102" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1wnk63aERf7/uTyT6okFjiq/Ayajw31Os+0y4XC6imY="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>Command</t>
   </si>
@@ -69,38 +78,766 @@
     <t>BgOff</t>
   </si>
   <si>
-    <t>Chapter1-2です</t>
-  </si>
-  <si>
     <t>Jump</t>
   </si>
   <si>
+    <t>Bgm</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM3</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Bg</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>普段の有希は、標準語を使う。</t>
+    <rPh sb="0" eb="2">
+      <t>フダン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ヒョウジュンゴ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>役者の訓練の一つだそうだ</t>
+    <rPh sb="0" eb="2">
+      <t>ヤクシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>クンレン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヒト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>けれど心から笑ったり怒ったりするとき、</t>
+    <rPh sb="3" eb="4">
+      <t>ココロ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ワラ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オコ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希は故郷.・福岡の、北九州弁を使う</t>
+    <rPh sb="3" eb="5">
+      <t>コキョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>フクオカ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>キタキュウシュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ベン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ごめん、ごめん！　遅くに呼び出して</t>
+    <rPh sb="9" eb="10">
+      <t>オソ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：夜のファミレス</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヨル</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>どうしても会ってしたい話があってさ</t>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハナシ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大事な話やけん、色んな人の、</t>
+    <rPh sb="0" eb="2">
+      <t>ダイジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハナシ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヒト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>特にあなたの意見を聞きたいな～って</t>
+    <rPh sb="0" eb="1">
+      <t>トク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イケン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こんな夢みたいな話、信じられんし、</t>
+    <rPh sb="3" eb="4">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ハナシ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>どうしていいか分からんくて……ははっ</t>
+    <rPh sb="7" eb="8">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希の動揺を見て、見当はついた</t>
+    <rPh sb="3" eb="5">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>崖から転がり落ちる有希の動画は、</t>
+    <rPh sb="0" eb="1">
+      <t>ガケ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>コロ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ドウガ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>色んな見出しでニュースサイトに載り、</t>
+    <rPh sb="0" eb="1">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ミダ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>今や有希は日本で一番有名な女子高生だ。</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ユウメイ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ジョシコウセイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……だから、有希の相談事の見当はつく</t>
+    <rPh sb="9" eb="11">
+      <t>ソウダン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ゴト</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>SNSで日本全国に拡散された</t>
+    <rPh sb="4" eb="6">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゼンコク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カクサン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「体当たりすぎる美少女」とか</t>
+    <rPh sb="1" eb="3">
+      <t>タイア</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ビショウジョ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>なんなら海外でも報じられたくらいだ</t>
+    <rPh sb="4" eb="6">
+      <t>カイガイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ホウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>実は東京の事務所から声がかかったの。</t>
+    <rPh sb="0" eb="1">
+      <t>ジツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ジムショ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コエ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>正式にウチと契約せんか……って</t>
+    <rPh sb="0" eb="2">
+      <t>セイシキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケイヤク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>この夜は、そうだった</t>
+    <rPh sb="2" eb="3">
+      <t>ヨル</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
     <t>*chapter0103_Start</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……そうだと思った</t>
+    <rPh sb="6" eb="7">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>マネージャーには</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>それで、相談事って？</t>
+    <rPh sb="4" eb="7">
+      <t>ソウダンゴト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Selection</t>
+  </si>
+  <si>
+    <t>浪川有希</t>
+  </si>
+  <si>
+    <t>浪川有希</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>通常</t>
+  </si>
+  <si>
+    <t>通常</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>はは、やっぱり分かるっちゃね。</t>
+    <rPh sb="7" eb="8">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……何て言うのかな、えっと……</t>
+    <rPh sb="2" eb="3">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>私、役者で成功したいって思ってた。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヤクシャ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ずっとそう思って、頑張って来た。</t>
+    <rPh sb="5" eb="6">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガンバ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも、いざ実現するってなると……</t>
+    <rPh sb="5" eb="7">
+      <t>ジツゲン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あはははっ……。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こんなの変だし、贅沢な悩みちゃね</t>
+    <rPh sb="4" eb="5">
+      <t>ヘン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゼイタク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ナヤ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>役者で食べてる人なんてごく一部で、</t>
+    <rPh sb="0" eb="2">
+      <t>ヤクシャ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イチブ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>芸能事務所に入るだけでも大変で……</t>
+    <rPh sb="0" eb="5">
+      <t>ゲイノウジムショ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイヘン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>なのに向こうから声がかかって、</t>
+    <rPh sb="3" eb="4">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>コエ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>凄く運がいいことなのに……なんでやろ？</t>
+    <rPh sb="0" eb="1">
+      <t>スゴ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希の気持ちは分かるような気がする</t>
+    <rPh sb="3" eb="5">
+      <t>キモ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>上京して、芸能人になる。</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ゲイノウジン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>それはつまり、人生を懸けるということだ</t>
+    <rPh sb="7" eb="9">
+      <t>ジンセイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>この数週間で起きた環境の激変もある。</t>
+    <rPh sb="2" eb="5">
+      <t>スウシュウカン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゲキヘン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>プレッシャーは凄いはずだ。 ……でも、</t>
+    <rPh sb="7" eb="8">
+      <t>スゴ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>夢を追うべきだよ</t>
+    <rPh sb="0" eb="1">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……有希ならできる。絶対</t>
+    <rPh sb="10" eb="12">
+      <t>ゼッタイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……だよね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こんな機会滅多にない。</t>
+    <rPh sb="3" eb="5">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>メッタ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>普通は一生に一回もないもん</t>
+    <rPh sb="0" eb="2">
+      <t>フツウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イッショウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イッカイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ありがとう。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そう言われると、私……</t>
+    <rPh sb="2" eb="3">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ワタシ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>頑張れそうな気がする。</t>
+    <rPh sb="0" eb="2">
+      <t>ガンバ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ううん、頑張れそうな気じゃなくて……</t>
+    <rPh sb="4" eb="6">
+      <t>ガンバ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-1-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-2-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-3-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-3-b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-3合流</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>決めた！私、頑張るよ！</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガンバ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>絶対に頑張るけんさ！</t>
+    <rPh sb="0" eb="2">
+      <t>ゼッタイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガンバ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そう力強く宣言すると、</t>
+    <rPh sb="2" eb="3">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センゲン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希は深呼吸をした</t>
+    <rPh sb="3" eb="6">
+      <t>シンコキュウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ふぅ……やっと落ち着けたかな。</t>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>この何週間も、ずっとバタバタしてて……</t>
+    <rPh sb="2" eb="5">
+      <t>ナンシュウカン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>急にこんな話まで来て凄く焦ったけど、</t>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ハナシ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>スゴ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アセ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>やっと落ち着いて、見えてきた気がする</t>
+    <rPh sb="3" eb="4">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>私が進む方向、やっと見えた。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>やっぱりあなたに相談してよかった</t>
+    <rPh sb="8" eb="10">
+      <t>ソウダン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -109,52 +846,53 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -344,28 +1082,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1055"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.5"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="7" width="5.13"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="9" width="37.75"/>
-    <col customWidth="1" min="10" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="12" width="11.38"/>
-    <col customWidth="1" min="13" max="26" width="8.0"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="7" width="5.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:12" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -403,7 +1141,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
+    <row r="2" spans="1:12" ht="13.5" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -411,11 +1149,11 @@
       <c r="H2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
+    <row r="3" spans="1:12" ht="13.5" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="4"/>
@@ -426,7 +1164,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
+    <row r="4" spans="1:12" ht="13.5" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -436,12 +1174,12 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="6">
-        <v>3.0</v>
+      <c r="H4" s="5">
+        <v>3</v>
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
+    <row r="5" spans="1:12" ht="13.5" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
@@ -455,618 +1193,920 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="B6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="7" t="s">
-        <v>17</v>
-      </c>
+    <row r="6" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="I12" s="1"/>
+    <row r="8" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B8" s="3"/>
+      <c r="I8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="13.5" customHeight="1">
+      <c r="I9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="13.5" customHeight="1">
+      <c r="I10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="13.5" customHeight="1">
+      <c r="I11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="13.5" customHeight="1">
+      <c r="I12" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="I13" s="1"/>
+    <row r="13" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" ht="13.5" customHeight="1">
+    <row r="14" spans="1:12" ht="13.5" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" ht="13.5" customHeight="1">
+    <row r="15" spans="1:12" ht="13.5" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="I16" s="1"/>
+    <row r="16" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" ht="13.5" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" ht="13.5" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="1"/>
+    <row r="17" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I19" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I20" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I21" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I22" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1">
       <c r="B23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="I23" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" ht="13.5" customHeight="1">
+    <row r="24" spans="1:10" ht="13.5" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="I24" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" ht="13.5" customHeight="1">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" ht="13.5" customHeight="1">
+    <row r="25" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="I25" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="I27" s="1"/>
+      <c r="I26" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="I27" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="I28" s="1"/>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I28" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" ht="13.5" customHeight="1">
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" ht="13.5" customHeight="1">
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" ht="13.5" customHeight="1">
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" ht="13.5" customHeight="1">
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" ht="13.5" customHeight="1">
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" ht="13.5" customHeight="1">
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" ht="13.5" customHeight="1">
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" ht="13.5" customHeight="1">
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" ht="13.5" customHeight="1">
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" ht="13.5" customHeight="1">
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" ht="13.5" customHeight="1">
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" ht="13.5" customHeight="1">
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" ht="13.5" customHeight="1">
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" ht="13.5" customHeight="1">
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" ht="13.5" customHeight="1">
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="1"/>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B31" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B39" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="s">
+        <v>50</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B40" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" t="s">
+        <v>50</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>50</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" t="s">
+        <v>50</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" t="s">
+        <v>50</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:10" ht="13.5" customHeight="1">
       <c r="B45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="I46" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="I45" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="I46" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" ht="13.5" customHeight="1">
+    <row r="47" spans="1:10" ht="13.5" customHeight="1">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
-      <c r="I47" s="1"/>
-    </row>
-    <row r="48" ht="13.5" customHeight="1">
+      <c r="I47" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A48" s="1"/>
       <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="I48" s="1"/>
+      <c r="I48" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" ht="13.5" customHeight="1">
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="I49" s="1"/>
+    <row r="49" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A49" s="1"/>
+      <c r="I49" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" ht="13.5" customHeight="1">
-      <c r="A51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" ht="13.5" customHeight="1">
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
+    <row r="50" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A50" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="I50" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A51" t="s">
+        <v>47</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="I51" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A52" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="I52" s="1"/>
     </row>
-    <row r="53" ht="13.5" customHeight="1">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" ht="13.5" customHeight="1">
+    <row r="53" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B53" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="13.5" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" ht="13.5" customHeight="1">
+      <c r="B55" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C55" t="s">
+        <v>50</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="I56" s="1"/>
     </row>
-    <row r="57" ht="13.5" customHeight="1">
+    <row r="57" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A57" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" ht="13.5" customHeight="1">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" ht="13.5" customHeight="1">
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" ht="13.5" customHeight="1">
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" ht="13.5" customHeight="1">
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
+    <row r="58" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B58" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B59" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B60" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H62" s="1"/>
       <c r="I62" s="1"/>
     </row>
-    <row r="63" ht="13.5" customHeight="1">
-      <c r="B63" s="1"/>
+    <row r="63" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A63" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="C63" s="1"/>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" ht="13.5" customHeight="1">
+    <row r="64" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B64" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="13.5" customHeight="1">
       <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" ht="13.5" customHeight="1">
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" ht="13.5" customHeight="1">
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" ht="13.5" customHeight="1">
+      <c r="B65" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C65" t="s">
+        <v>50</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="13.5" customHeight="1">
+      <c r="H66" s="1"/>
+      <c r="I66" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I67" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="13.5" customHeight="1">
       <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" ht="13.5" customHeight="1">
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" ht="13.5" customHeight="1">
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="I71" s="1"/>
-    </row>
-    <row r="72" ht="13.5" customHeight="1">
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" ht="13.5" customHeight="1">
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74" ht="13.5" customHeight="1">
+      <c r="B68" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68" t="s">
+        <v>50</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B70" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70" t="s">
+        <v>50</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B71" t="s">
+        <v>48</v>
+      </c>
+      <c r="C71" t="s">
+        <v>50</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B72" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B73" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="13.5" customHeight="1">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="I74" s="1"/>
     </row>
-    <row r="75" ht="13.5" customHeight="1">
+    <row r="75" spans="1:10" ht="13.5" customHeight="1">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="I75" s="1"/>
-    </row>
-    <row r="76" ht="13.5" customHeight="1">
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" ht="13.5" customHeight="1">
       <c r="I76" s="1"/>
     </row>
-    <row r="77" ht="13.5" customHeight="1">
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
+    <row r="77" spans="1:10" ht="13.5" customHeight="1">
       <c r="I77" s="1"/>
     </row>
-    <row r="78" ht="13.5" customHeight="1">
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
+    <row r="78" spans="1:10" ht="13.5" customHeight="1">
       <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-    </row>
-    <row r="79" ht="13.5" customHeight="1">
+    </row>
+    <row r="79" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
       <c r="I79" s="1"/>
-    </row>
-    <row r="80" ht="13.5" customHeight="1">
+      <c r="J79" s="1"/>
+    </row>
+    <row r="80" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
       <c r="I80" s="1"/>
-    </row>
-    <row r="81" ht="13.5" customHeight="1">
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="1"/>
+      <c r="J80" s="1"/>
+    </row>
+    <row r="81" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A81" s="1"/>
+    </row>
+    <row r="82" spans="1:9" ht="13.5" customHeight="1">
       <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="1"/>
+    </row>
+    <row r="83" spans="1:9" ht="13.5" customHeight="1">
       <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
       <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" ht="13.5" customHeight="1">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" ht="13.5" customHeight="1">
+    </row>
+    <row r="84" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:9" ht="13.5" customHeight="1">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="I85" s="1"/>
     </row>
-    <row r="86" ht="13.5" customHeight="1">
+    <row r="86" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A86" s="1"/>
       <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="I86" s="1"/>
-    </row>
-    <row r="87" ht="13.5" customHeight="1">
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88" ht="13.5" customHeight="1">
+    </row>
+    <row r="87" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A87" s="1"/>
+    </row>
+    <row r="88" spans="1:9" ht="13.5" customHeight="1">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="I88" s="1"/>
     </row>
-    <row r="89" ht="13.5" customHeight="1">
-      <c r="A89" s="1"/>
+    <row r="89" spans="1:9" ht="13.5" customHeight="1">
       <c r="B89" s="1"/>
-    </row>
-    <row r="90" ht="13.5" customHeight="1">
-      <c r="A90" s="1"/>
-    </row>
-    <row r="91" ht="13.5" customHeight="1">
+      <c r="C89" s="1"/>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91" spans="1:9" ht="13.5" customHeight="1">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="I91" s="1"/>
     </row>
-    <row r="92" ht="13.5" customHeight="1">
+    <row r="92" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A92" s="1"/>
       <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93" ht="13.5" customHeight="1">
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="I93" s="1"/>
-    </row>
-    <row r="94" ht="13.5" customHeight="1">
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
+    </row>
+    <row r="93" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A93" s="1"/>
+    </row>
+    <row r="94" spans="1:9" ht="13.5" customHeight="1">
       <c r="I94" s="1"/>
     </row>
-    <row r="95" ht="13.5" customHeight="1">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-    </row>
-    <row r="96" ht="13.5" customHeight="1">
+    <row r="95" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I95" s="1"/>
+    </row>
+    <row r="96" spans="1:9" ht="13.5" customHeight="1">
       <c r="A96" s="1"/>
-    </row>
-    <row r="97" ht="13.5" customHeight="1">
+      <c r="B96" s="1"/>
+      <c r="I96" s="1"/>
+    </row>
+    <row r="97" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A97" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H97" s="1"/>
       <c r="I97" s="1"/>
     </row>
-    <row r="98" ht="13.5" customHeight="1">
+    <row r="98" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
       <c r="I98" s="1"/>
     </row>
-    <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="1"/>
+    <row r="99" spans="1:10" ht="13.5" customHeight="1">
       <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
       <c r="I99" s="1"/>
     </row>
-    <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="1"/>
-      <c r="H100" s="1"/>
+    <row r="100" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
       <c r="I100" s="1"/>
     </row>
-    <row r="101" ht="13.5" customHeight="1">
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
+    <row r="101" spans="1:10" ht="13.5" customHeight="1">
       <c r="I101" s="1"/>
     </row>
-    <row r="102" ht="13.5" customHeight="1">
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
+    <row r="102" spans="1:10" ht="13.5" customHeight="1">
       <c r="I102" s="1"/>
     </row>
-    <row r="103" ht="13.5" customHeight="1">
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
+    <row r="103" spans="1:10" ht="13.5" customHeight="1">
       <c r="I103" s="1"/>
     </row>
-    <row r="104" ht="13.5" customHeight="1">
+    <row r="104" spans="1:10" ht="13.5" customHeight="1">
       <c r="I104" s="1"/>
     </row>
-    <row r="105" ht="13.5" customHeight="1">
+    <row r="105" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
       <c r="I105" s="1"/>
     </row>
-    <row r="106" ht="13.5" customHeight="1">
+    <row r="106" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
       <c r="I106" s="1"/>
     </row>
-    <row r="107" ht="13.5" customHeight="1">
+    <row r="107" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
       <c r="I107" s="1"/>
     </row>
-    <row r="108" ht="13.5" customHeight="1">
+    <row r="108" spans="1:10" ht="13.5" customHeight="1">
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="I108" s="1"/>
     </row>
-    <row r="109" ht="13.5" customHeight="1">
+    <row r="109" spans="1:10" ht="13.5" customHeight="1">
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
       <c r="I109" s="1"/>
     </row>
-    <row r="110" ht="13.5" customHeight="1">
+    <row r="110" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A110" s="1"/>
       <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
       <c r="I110" s="1"/>
-    </row>
-    <row r="111" ht="13.5" customHeight="1">
+      <c r="J110" s="1"/>
+    </row>
+    <row r="111" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A111" s="1"/>
       <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
       <c r="I111" s="1"/>
-    </row>
-    <row r="112" ht="13.5" customHeight="1">
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
+      <c r="J111" s="1"/>
+    </row>
+    <row r="112" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A112" s="1"/>
       <c r="I112" s="1"/>
-    </row>
-    <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" s="1"/>
+      <c r="J112" s="1"/>
+    </row>
+    <row r="113" spans="1:10" ht="13.5" customHeight="1">
       <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
       <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-    </row>
-    <row r="114" ht="13.5" customHeight="1">
+    </row>
+    <row r="114" spans="1:10" ht="13.5" customHeight="1">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" ht="13.5" customHeight="1">
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1">
       <c r="A115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
-    </row>
-    <row r="116" ht="13.5" customHeight="1">
+    </row>
+    <row r="116" spans="1:10" ht="13.5" customHeight="1">
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="I116" s="1"/>
     </row>
-    <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" s="1"/>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1">
       <c r="B117" s="1"/>
-    </row>
-    <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" ht="13.5" customHeight="1">
+      <c r="C117" s="1"/>
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A119" s="1"/>
       <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="I119" s="1"/>
-    </row>
-    <row r="120" ht="13.5" customHeight="1">
+    </row>
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A120" s="1"/>
       <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
       <c r="I120" s="1"/>
-    </row>
-    <row r="121" ht="13.5" customHeight="1">
+      <c r="J120" s="1"/>
+    </row>
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="I121" s="1"/>
     </row>
-    <row r="122" ht="13.5" customHeight="1">
-      <c r="A122" s="1"/>
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="B122" s="1"/>
-    </row>
-    <row r="123" ht="13.5" customHeight="1">
+      <c r="C122" s="1"/>
+      <c r="I122" s="1"/>
+    </row>
+    <row r="123" spans="1:10" ht="13.5" customHeight="1">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-    </row>
-    <row r="124" ht="13.5" customHeight="1">
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="I124" s="1"/>
-    </row>
-    <row r="125" ht="13.5" customHeight="1">
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
+    </row>
+    <row r="124" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A124" s="1"/>
+    </row>
+    <row r="125" spans="1:10" ht="13.5" customHeight="1">
       <c r="I125" s="1"/>
     </row>
-    <row r="126" ht="13.5" customHeight="1">
+    <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-    </row>
-    <row r="127" ht="13.5" customHeight="1">
+    </row>
+    <row r="127" spans="1:10" ht="13.5" customHeight="1">
       <c r="A127" s="1"/>
     </row>
-    <row r="128" ht="13.5" customHeight="1">
+    <row r="128" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="H128" s="1"/>
       <c r="I128" s="1"/>
     </row>
-    <row r="129" ht="13.5" customHeight="1">
+    <row r="129" spans="1:9" ht="13.5" customHeight="1">
       <c r="A129" s="1"/>
-    </row>
-    <row r="130" ht="13.5" customHeight="1">
-      <c r="A130" s="1"/>
-    </row>
-    <row r="131" ht="13.5" customHeight="1">
-      <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="H131" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+    </row>
+    <row r="130" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I130" s="1"/>
+    </row>
+    <row r="131" spans="1:9" ht="13.5" customHeight="1">
       <c r="I131" s="1"/>
     </row>
-    <row r="132" ht="13.5" customHeight="1">
-      <c r="A132" s="1"/>
-      <c r="H132" s="1"/>
+    <row r="132" spans="1:9" ht="13.5" customHeight="1">
       <c r="I132" s="1"/>
     </row>
-    <row r="133" ht="13.5" customHeight="1">
+    <row r="133" spans="1:9" ht="13.5" customHeight="1">
       <c r="I133" s="1"/>
     </row>
-    <row r="134" ht="13.5" customHeight="1">
+    <row r="134" spans="1:9" ht="13.5" customHeight="1">
       <c r="I134" s="1"/>
     </row>
-    <row r="135" ht="13.5" customHeight="1">
+    <row r="135" spans="1:9" ht="13.5" customHeight="1">
       <c r="I135" s="1"/>
     </row>
-    <row r="136" ht="13.5" customHeight="1">
+    <row r="136" spans="1:9" ht="13.5" customHeight="1">
       <c r="I136" s="1"/>
     </row>
-    <row r="137" ht="13.5" customHeight="1">
-      <c r="I137" s="1"/>
-    </row>
-    <row r="138" ht="13.5" customHeight="1">
-      <c r="I138" s="1"/>
-    </row>
-    <row r="139" ht="13.5" customHeight="1">
-      <c r="I139" s="1"/>
-    </row>
-    <row r="140" ht="13.5" customHeight="1"/>
-    <row r="141" ht="13.5" customHeight="1"/>
-    <row r="142" ht="13.5" customHeight="1"/>
-    <row r="143" ht="13.5" customHeight="1"/>
-    <row r="144" ht="13.5" customHeight="1"/>
+    <row r="137" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="138" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="139" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="140" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="141" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="142" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="143" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="144" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="145" ht="13.5" customHeight="1"/>
     <row r="146" ht="13.5" customHeight="1"/>
     <row r="147" ht="13.5" customHeight="1"/>
@@ -1978,13 +3018,9 @@
     <row r="1053" ht="13.5" customHeight="1"/>
     <row r="1054" ht="13.5" customHeight="1"/>
     <row r="1055" ht="13.5" customHeight="1"/>
-    <row r="1056" ht="13.5" customHeight="1"/>
-    <row r="1057" ht="13.5" customHeight="1"/>
-    <row r="1058" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/test260903/chapter0102.xlsx
+++ b/Assets/test260903/chapter0102.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B31455B6-AB2D-4FE4-AE6B-8D018193DB43}"/>
+  <xr:revisionPtr revIDLastSave="779" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2243162-63C2-478F-A851-48308EC26EDB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="91">
   <si>
     <t>Command</t>
   </si>
@@ -90,77 +90,6 @@
   </si>
   <si>
     <t>Bg</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>普段の有希は、標準語を使う。</t>
-    <rPh sb="0" eb="2">
-      <t>フダン</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>ヒョウジュンゴ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ツカ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>役者の訓練の一つだそうだ</t>
-    <rPh sb="0" eb="2">
-      <t>ヤクシャ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>クンレン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ヒト</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>けれど心から笑ったり怒ったりするとき、</t>
-    <rPh sb="3" eb="4">
-      <t>ココロ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ワラ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>オコ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>有希は故郷.・福岡の、北九州弁を使う</t>
-    <rPh sb="3" eb="5">
-      <t>コキョウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>フクオカ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>キタキュウシュウ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ベン</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ツカ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>ごめん、ごめん！　遅くに呼び出して</t>
-    <rPh sb="9" eb="10">
-      <t>オソ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ダ</t>
-    </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -174,628 +103,624 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>どうしても会ってしたい話があってさ</t>
+    <t>*chapter0103_Start</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>浪川有希</t>
+  </si>
+  <si>
+    <t>浪川有希</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>通常</t>
+  </si>
+  <si>
+    <t>通常</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……だよね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-1-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-2-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-3-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-3-b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-3合流</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>普段の有希は、標準語を使う。
+役者の訓練の一つだそうだ</t>
+    <rPh sb="0" eb="2">
+      <t>フダン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ヒョウジュンゴ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">けれど心から笑ったり怒ったりするとき、
+有希は故郷.・福岡の、北九州弁を使う    </t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>この夜は、そうだった</t>
+  </si>
+  <si>
+    <t>ごめん、ごめん！　遅くに呼び出して
+どうしても会ってしたい話があってさ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大事な話やけん、色んな人の、
+特にあなたの意見を聞きたいな～って</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こんな夢みたいな話、信じられんし
+どうしていいか分からんくて……ははっ、</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希の動揺を見て、見当はついた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>崖から転がり落ちる有希の動画は、
+SNSで日本全国に拡散された</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「体当たりすぎる美少女」とか
+「女優魂が凄い現役女子高生」とか</t>
+    <rPh sb="16" eb="19">
+      <t>ジョユウダマシイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>スゴ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ゲンエキ</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>ジョシコウセイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>色んな見出しでニュースサイトに載り、
+なんなら海外でも報じられたくらいだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>今や有希は日本で一番有名な女子高生だ。
+……だから、有希の相談事の見当はつく</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>実は東京の事務所から声がかかったの。
+正式にウチと契約せんか……って</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">浪川有希
+</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">通常
+</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……そうだと思った</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>はは、やっぱり分かるっちゃね。
+マネージャーには</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>それで、相談事って？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……何て言うのかな、えっと……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>私、役者で成功したいって思ってた。
+こういうチャンスをずっと待ってた</t>
+    <rPh sb="30" eb="31">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ずっとそう思って、頑張って来た。
+でも、いざ実現するってなると……</t>
     <rPh sb="5" eb="6">
-      <t>ア</t>
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガンバ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジツゲン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あはははっ……。
+こんなの変だし、贅沢な悩みちゃね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>役者で食べてる人なんてごく一部で、
+芸能事務所に入るだけでも大変で……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>なのに向こうから声がかかって、
+凄く運がいいことなのに……なんでやろ？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>なんでか……不安でさ。
+凄く、怖いいんちゃね……</t>
+    <rPh sb="6" eb="8">
+      <t>フアン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>スゴ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>コワ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希の気持ちは分かるような気がする</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>上京して、芸能人になる。
+それはつまり、人生を懸けるということだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希の中で漠然とした「夢」だった役者が、
+ハッキリとした実像を待つ「仕事」になった</t>
+    <rPh sb="3" eb="4">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>バクゼン</t>
     </rPh>
     <rPh sb="11" eb="12">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヤクシャ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジツゾウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>シゴト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>この数週間で起きた環境の激変もある。
+プレッシャーは凄いはずだ。 ……でも、</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>夢を追うべきだよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……有希ならできる。絶対</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こんな機会滅多にない。
+普通は一生に一回もないもん</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Jump</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ありがとう。
+そう言われると、私……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>頑張れそうな気がする。
+ううん、頑張れそうな気じゃなくて……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>決めた！私、頑張るよ！
+絶対に頑張るけんさ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そう力強く宣言すると、
+有希は深呼吸をした</t>
+    <rPh sb="2" eb="3">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センゲン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ふぅ……やっと落ち着けたかな。
+この何週間も、ずっとバタバタしてて……</t>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>急にこんな話まで来て凄く焦ったけど、
+やっと落ち着いて、見えてきた気がする</t>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
       <t>ハナシ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>大事な話やけん、色んな人の、</t>
-    <rPh sb="0" eb="2">
-      <t>ダイジ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ハナシ</t>
-    </rPh>
     <rPh sb="8" eb="9">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ヒト</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>特にあなたの意見を聞きたいな～って</t>
-    <rPh sb="0" eb="1">
-      <t>トク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イケン</t>
-    </rPh>
-    <rPh sb="9" eb="10">
       <t>キ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>こんな夢みたいな話、信じられんし、</t>
-    <rPh sb="3" eb="4">
-      <t>ユメ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ハナシ</t>
-    </rPh>
     <rPh sb="10" eb="11">
-      <t>シン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>どうしていいか分からんくて……ははっ</t>
-    <rPh sb="7" eb="8">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>有希の動揺を見て、見当はついた</t>
-    <rPh sb="3" eb="5">
-      <t>ドウヨウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ケントウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>崖から転がり落ちる有希の動画は、</t>
-    <rPh sb="0" eb="1">
-      <t>ガケ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>コロ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ドウガ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>色んな見出しでニュースサイトに載り、</t>
-    <rPh sb="0" eb="1">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ミダ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ノ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>今や有希は日本で一番有名な女子高生だ。</t>
-    <rPh sb="0" eb="1">
-      <t>イマ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ニホン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>イチバン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ユウメイ</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>ジョシコウセイ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>……だから、有希の相談事の見当はつく</t>
-    <rPh sb="9" eb="11">
-      <t>ソウダン</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ゴト</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ケントウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>SNSで日本全国に拡散された</t>
-    <rPh sb="4" eb="6">
-      <t>ニホン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ゼンコク</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カクサン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>「体当たりすぎる美少女」とか</t>
-    <rPh sb="1" eb="3">
-      <t>タイア</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>ビショウジョ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>なんなら海外でも報じられたくらいだ</t>
-    <rPh sb="4" eb="6">
-      <t>カイガイ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ホウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>実は東京の事務所から声がかかったの。</t>
-    <rPh sb="0" eb="1">
-      <t>ジツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トウキョウ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ジムショ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>コエ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>正式にウチと契約せんか……って</t>
-    <rPh sb="0" eb="2">
-      <t>セイシキ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ケイヤク</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>この夜は、そうだった</t>
-    <rPh sb="2" eb="3">
-      <t>ヨル</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>*chapter0103_Start</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>……そうだと思った</t>
-    <rPh sb="6" eb="7">
-      <t>オモ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>マネージャーには</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>それで、相談事って？</t>
-    <rPh sb="4" eb="7">
-      <t>ソウダンゴト</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>Selection</t>
-  </si>
-  <si>
-    <t>浪川有希</t>
-  </si>
-  <si>
-    <t>浪川有希</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>通常</t>
-  </si>
-  <si>
-    <t>通常</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>はは、やっぱり分かるっちゃね。</t>
-    <rPh sb="7" eb="8">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>……何て言うのかな、えっと……</t>
-    <rPh sb="2" eb="3">
-      <t>ナン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>私、役者で成功したいって思ってた。</t>
+      <t>スゴ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アセ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>私が進む方向、やっと見えた。
+やっぱりあなたに相談してよかった</t>
     <rPh sb="0" eb="1">
       <t>ワタシ</t>
     </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヤクシャ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>セイコウ</t>
+    <rPh sb="2" eb="3">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>マネージャー。
+私、東京で頑張ってくるよ</t>
+    <rPh sb="8" eb="9">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガンバ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あの頃の……子どもの時の約束通り、
+2人で夢を叶えようよ！</t>
+    <rPh sb="2" eb="3">
+      <t>コロ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヤクソク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ドオ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カナ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希の目が、ハッキリと輝いていた</t>
+    <rPh sb="3" eb="4">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カガヤ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>何がなんでもやり遂げる。
+そういう決意を固めた時の目だ</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ケツイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>子役の仕事を始めた時、
+初めてドラマや舞台の本番を迎える時……</t>
+    <rPh sb="0" eb="2">
+      <t>コヤク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>トキ</t>
     </rPh>
     <rPh sb="12" eb="13">
-      <t>オモ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>ずっとそう思って、頑張って来た。</t>
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ブタイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ホンバン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ムカ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希はこの目をして、絶対に成功させる。
+きっと東京でだって上手くいくはずだ</t>
     <rPh sb="5" eb="6">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ガンバ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>でも、いざ実現するってなると……</t>
-    <rPh sb="5" eb="7">
-      <t>ジツゲン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>あはははっ……。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>こんなの変だし、贅沢な悩みちゃね</t>
-    <rPh sb="4" eb="5">
-      <t>ヘン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ゼイタク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ナヤ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>役者で食べてる人なんてごく一部で、</t>
-    <rPh sb="0" eb="2">
-      <t>ヤクシャ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>イチブ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>芸能事務所に入るだけでも大変で……</t>
-    <rPh sb="0" eb="5">
-      <t>ゲイノウジムショ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ハイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>タイヘン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>なのに向こうから声がかかって、</t>
-    <rPh sb="3" eb="4">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>コエ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>凄く運がいいことなのに……なんでやろ？</t>
-    <rPh sb="0" eb="1">
-      <t>スゴ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ウン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>有希の気持ちは分かるような気がする</t>
-    <rPh sb="3" eb="5">
-      <t>キモ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>上京して、芸能人になる。</t>
-    <rPh sb="0" eb="2">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ゲイノウジン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>それはつまり、人生を懸けるということだ</t>
-    <rPh sb="7" eb="9">
-      <t>ジンセイ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>この数週間で起きた環境の激変もある。</t>
-    <rPh sb="2" eb="5">
-      <t>スウシュウカン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ゲキヘン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>プレッシャーは凄いはずだ。 ……でも、</t>
-    <rPh sb="7" eb="8">
-      <t>スゴ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>夢を追うべきだよ</t>
-    <rPh sb="0" eb="1">
-      <t>ユメ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>……有希ならできる。絶対</t>
+      <t>メ</t>
+    </rPh>
     <rPh sb="10" eb="12">
       <t>ゼッタイ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>……だよね</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>こんな機会滅多にない。</t>
-    <rPh sb="3" eb="5">
-      <t>キカイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>メッタ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>普通は一生に一回もないもん</t>
+    <rPh sb="13" eb="15">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ウマ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>しかし、それはそれとして……
+子どもの時の約束って何だろう？</t>
+    <rPh sb="15" eb="16">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヤクソク</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あれ？
+どうかしたの、マネージャー？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-4-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>子どもの時の約束って？</t>
+    <rPh sb="0" eb="1">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヤクソク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ええっ！　覚えてないの？</t>
+    <rPh sb="5" eb="6">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あれは幼稚園の頃……あなたのことを、
+マネージャーって呼び出したキカッケだよ</t>
+    <rPh sb="3" eb="6">
+      <t>ヨウチエン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>コロ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あなたは作家になるって言って、
+だったら私は、役者になるって言ったの</t>
+    <rPh sb="4" eb="6">
+      <t>サッカ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヤクシャ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そしたらあなたが本が、
+映画やドラマになったら私が演じるって</t>
+    <rPh sb="8" eb="9">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>エイガ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>で、そうなった時は自分のことを
+センセーと呼んでくれって</t>
+    <rPh sb="7" eb="8">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>小説家になれないうちは、
+マネージャーと呼んでいいと言って……</t>
     <rPh sb="0" eb="2">
-      <t>フツウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>イッショウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イッカイ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>ありがとう。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>そう言われると、私……</t>
+      <t>ショウセツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イエ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そう言う約束だったんだけど、
+まさか忘れたの？</t>
     <rPh sb="2" eb="3">
       <t>イ</t>
     </rPh>
-    <rPh sb="8" eb="9">
-      <t>ワタシ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>頑張れそうな気がする。</t>
-    <rPh sb="0" eb="2">
-      <t>ガンバ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>ううん、頑張れそうな気じゃなくて……</t>
     <rPh sb="4" eb="6">
-      <t>ガンバ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>*選択肢0102-1-a</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>*選択肢0102-2-a</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>*選択肢0102-3-a</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>*選択肢0102-3-b</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>*選択肢0102-3合流</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>決めた！私、頑張るよ！</t>
-    <rPh sb="0" eb="1">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ガンバ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>絶対に頑張るけんさ！</t>
-    <rPh sb="0" eb="2">
-      <t>ゼッタイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ガンバ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>そう力強く宣言すると、</t>
-    <rPh sb="2" eb="3">
-      <t>チカラ</t>
-    </rPh>
+      <t>ヤクソク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ワス</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>えっ、僕……そんなこと言ったの？</t>
     <rPh sb="3" eb="4">
-      <t>ツヨ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>センゲン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>有希は深呼吸をした</t>
-    <rPh sb="3" eb="6">
-      <t>シンコキュウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>ふぅ……やっと落ち着けたかな。</t>
-    <rPh sb="7" eb="8">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ツ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>この何週間も、ずっとバタバタしてて……</t>
-    <rPh sb="2" eb="5">
-      <t>ナンシュウカン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>急にこんな話まで来て凄く焦ったけど、</t>
-    <rPh sb="0" eb="1">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ハナシ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>スゴ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>アセ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>やっと落ち着いて、見えてきた気がする</t>
-    <rPh sb="3" eb="4">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>私が進む方向、やっと見えた。</t>
-    <rPh sb="0" eb="1">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>スス</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ホウコウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>やっぱりあなたに相談してよかった</t>
-    <rPh sb="8" eb="10">
-      <t>ソウダン</t>
+      <t>ボク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>イ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -861,7 +786,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -869,6 +794,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1096,7 +1051,7 @@
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="7" width="5.109375" customWidth="1"/>
     <col min="8" max="8" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="9" max="9" width="43.33203125" style="7" customWidth="1"/>
     <col min="10" max="10" width="8.21875" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
     <col min="12" max="12" width="11.33203125" customWidth="1"/>
@@ -1128,7 +1083,7 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1162,7 +1117,7 @@
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="1"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:12" ht="13.5" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -1177,7 +1132,7 @@
       <c r="H4" s="5">
         <v>3</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="13.5" customHeight="1">
       <c r="A5" s="4" t="s">
@@ -1190,7 +1145,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="1"/>
+      <c r="I5" s="6"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:12" ht="13.5" customHeight="1">
@@ -1198,663 +1153,657 @@
         <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="I6" s="6"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:12" ht="13.5" customHeight="1">
+    <row r="7" spans="1:12" ht="13.8" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:12" ht="13.5" customHeight="1">
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" ht="26.4">
       <c r="B8" s="3"/>
-      <c r="I8" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="13.5" customHeight="1">
-      <c r="I9" s="1" t="s">
-        <v>22</v>
+      <c r="I8" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="27.6" customHeight="1">
+      <c r="I9" s="9" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="13.5" customHeight="1">
-      <c r="I10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="13.5" customHeight="1">
-      <c r="I11" s="1" t="s">
+      <c r="I10" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="29.4" customHeight="1">
+      <c r="B11" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="25.2" customHeight="1">
+      <c r="B12" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" ht="27" customHeight="1">
+      <c r="B13" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="I14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" ht="27.6" customHeight="1">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="I15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:12" ht="28.2" customHeight="1">
+      <c r="I16" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" ht="27.6" customHeight="1">
+      <c r="I17" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="27.6" customHeight="1">
+      <c r="I18" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B19" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="13.5" customHeight="1">
-      <c r="I12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" ht="13.5" customHeight="1">
-      <c r="B13" t="s">
+      <c r="C19" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="I20" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B22" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="I23" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1" t="s">
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" ht="13.2" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="29.4" customHeight="1">
+      <c r="B26" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B27" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10" ht="27" customHeight="1">
+      <c r="B28" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B29" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="27" customHeight="1">
+      <c r="A30" s="3"/>
+      <c r="B30" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B31" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="I32" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="27" customHeight="1">
+      <c r="B33" s="3"/>
+      <c r="I33" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="27" customHeight="1">
+      <c r="A34" s="3"/>
+      <c r="I34" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="I35" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A36" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="I14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1" t="s">
+      <c r="B36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="I36" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A37" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:12" ht="13.5" customHeight="1">
-      <c r="B16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="1" t="s">
+      <c r="B37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="I37" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A38" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I19" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I20" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I21" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I22" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="I23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="I24" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A25" s="1"/>
-      <c r="I25" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="I26" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="I27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I28" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A29" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A30" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B31" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B32" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A33" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A34" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B35" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B36" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B37" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B38" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" t="s">
-        <v>50</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="B38" s="3"/>
+      <c r="I38" s="8"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1">
       <c r="B39" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" t="s">
-        <v>50</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B40" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>58</v>
+        <v>24</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B40" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B41" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" t="s">
-        <v>50</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>59</v>
-      </c>
+      <c r="A41" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="8"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B42" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" t="s">
-        <v>50</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B43" t="s">
-        <v>48</v>
-      </c>
-      <c r="C43" t="s">
-        <v>50</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B44" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" t="s">
-        <v>50</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>62</v>
+      <c r="A42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="8"/>
+    </row>
+    <row r="43" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B43" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="26.4" customHeight="1">
+      <c r="B44" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B45" s="1"/>
+      <c r="A45" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="C45" s="1"/>
-      <c r="I45" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="I45" s="8"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A46" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
-      <c r="I46" s="3" t="s">
-        <v>64</v>
-      </c>
+      <c r="I46" s="8"/>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="I47" s="3" t="s">
-        <v>65</v>
+    <row r="47" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B47" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="1:10" ht="13.5" customHeight="1">
+    <row r="48" spans="1:10" ht="27.6" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
-      <c r="I48" s="3" t="s">
-        <v>66</v>
+      <c r="I48" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:10" ht="13.5" customHeight="1">
+    <row r="49" spans="1:10" ht="28.2" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="I49" s="3" t="s">
-        <v>67</v>
+      <c r="B49" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A50" t="s">
-        <v>47</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C50" s="1"/>
-      <c r="I50" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="I51" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A52" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B53" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>70</v>
+    <row r="50" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B50" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B51" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A52" s="1"/>
+      <c r="B52" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B53" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B54" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="I54" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="27.6" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="B55" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C55" t="s">
-        <v>50</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A56" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A57" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="B55" s="1"/>
+      <c r="I55" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="I56" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A57" s="3"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B58" s="1" t="s">
+      <c r="I57" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="I58" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B59" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A60" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B59" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="13.5" customHeight="1">
       <c r="B60" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
+      </c>
+      <c r="C60" s="1"/>
+      <c r="I60" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="A61" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" s="1"/>
+      <c r="C61" s="3"/>
+      <c r="I61" s="6"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A62" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
-        <v>81</v>
+        <v>24</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-    </row>
-    <row r="63" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A63" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" s="1"/>
-      <c r="I63" s="1"/>
-    </row>
-    <row r="64" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B64" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I62" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A63" s="1"/>
+      <c r="B63" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B64" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="27.6" customHeight="1">
       <c r="A65" s="1"/>
-      <c r="B65" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C65" t="s">
-        <v>50</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B65" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="27" customHeight="1">
+      <c r="B66" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="H66" s="1"/>
-      <c r="I66" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I67" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I66" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B67" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="28.2" customHeight="1">
       <c r="A68" s="1"/>
-      <c r="B68" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C68" t="s">
-        <v>50</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>86</v>
+      <c r="B68" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B69" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B70" t="s">
-        <v>48</v>
-      </c>
-      <c r="C70" t="s">
-        <v>50</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
+      <c r="I69" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="13.5" customHeight="1"/>
     <row r="71" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B71" t="s">
-        <v>48</v>
-      </c>
-      <c r="C71" t="s">
-        <v>50</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B72" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
+      <c r="I71" s="6"/>
+    </row>
+    <row r="72" spans="1:10" ht="13.5" customHeight="1"/>
     <row r="73" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B73" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="I73" s="6"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
-      <c r="I74" s="1"/>
+      <c r="I74" s="6"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
-      <c r="I75" s="1"/>
+      <c r="I75" s="6"/>
       <c r="J75" s="1"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I76" s="1"/>
+      <c r="I76" s="6"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I77" s="1"/>
+      <c r="I77" s="6"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I78" s="1"/>
+      <c r="I78" s="6"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="I79" s="1"/>
+      <c r="I79" s="6"/>
       <c r="J79" s="1"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
-      <c r="I80" s="1"/>
+      <c r="I80" s="6"/>
       <c r="J80" s="1"/>
     </row>
     <row r="81" spans="1:9" ht="13.5" customHeight="1">
@@ -1863,22 +1812,22 @@
     <row r="82" spans="1:9" ht="13.5" customHeight="1">
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
-      <c r="I82" s="1"/>
+      <c r="I82" s="6"/>
     </row>
     <row r="83" spans="1:9" ht="13.5" customHeight="1">
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
-      <c r="I83" s="1"/>
+      <c r="I83" s="6"/>
     </row>
     <row r="84" spans="1:9" ht="13.5" customHeight="1">
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
-      <c r="I84" s="1"/>
+      <c r="I84" s="6"/>
     </row>
     <row r="85" spans="1:9" ht="13.5" customHeight="1">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
-      <c r="I85" s="1"/>
+      <c r="I85" s="6"/>
     </row>
     <row r="86" spans="1:9" ht="13.5" customHeight="1">
       <c r="A86" s="1"/>
@@ -1890,22 +1839,22 @@
     <row r="88" spans="1:9" ht="13.5" customHeight="1">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
-      <c r="I88" s="1"/>
+      <c r="I88" s="6"/>
     </row>
     <row r="89" spans="1:9" ht="13.5" customHeight="1">
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
-      <c r="I89" s="1"/>
+      <c r="I89" s="6"/>
     </row>
     <row r="90" spans="1:9" ht="13.5" customHeight="1">
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
-      <c r="I90" s="1"/>
+      <c r="I90" s="6"/>
     </row>
     <row r="91" spans="1:9" ht="13.5" customHeight="1">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
-      <c r="I91" s="1"/>
+      <c r="I91" s="6"/>
     </row>
     <row r="92" spans="1:9" ht="13.5" customHeight="1">
       <c r="A92" s="1"/>
@@ -1915,99 +1864,99 @@
       <c r="A93" s="1"/>
     </row>
     <row r="94" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I94" s="1"/>
+      <c r="I94" s="6"/>
     </row>
     <row r="95" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I95" s="1"/>
+      <c r="I95" s="6"/>
     </row>
     <row r="96" spans="1:9" ht="13.5" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
-      <c r="I96" s="1"/>
+      <c r="I96" s="6"/>
     </row>
     <row r="97" spans="1:10" ht="13.5" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
+      <c r="I97" s="6"/>
     </row>
     <row r="98" spans="1:10" ht="13.5" customHeight="1">
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
-      <c r="I98" s="1"/>
+      <c r="I98" s="6"/>
     </row>
     <row r="99" spans="1:10" ht="13.5" customHeight="1">
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
-      <c r="I99" s="1"/>
+      <c r="I99" s="6"/>
     </row>
     <row r="100" spans="1:10" ht="13.5" customHeight="1">
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
-      <c r="I100" s="1"/>
+      <c r="I100" s="6"/>
     </row>
     <row r="101" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I101" s="1"/>
+      <c r="I101" s="6"/>
     </row>
     <row r="102" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I102" s="1"/>
+      <c r="I102" s="6"/>
     </row>
     <row r="103" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I103" s="1"/>
+      <c r="I103" s="6"/>
     </row>
     <row r="104" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I104" s="1"/>
+      <c r="I104" s="6"/>
     </row>
     <row r="105" spans="1:10" ht="13.5" customHeight="1">
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
-      <c r="I105" s="1"/>
+      <c r="I105" s="6"/>
     </row>
     <row r="106" spans="1:10" ht="13.5" customHeight="1">
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
-      <c r="I106" s="1"/>
+      <c r="I106" s="6"/>
     </row>
     <row r="107" spans="1:10" ht="13.5" customHeight="1">
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
-      <c r="I107" s="1"/>
+      <c r="I107" s="6"/>
     </row>
     <row r="108" spans="1:10" ht="13.5" customHeight="1">
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
-      <c r="I108" s="1"/>
+      <c r="I108" s="6"/>
     </row>
     <row r="109" spans="1:10" ht="13.5" customHeight="1">
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
-      <c r="I109" s="1"/>
+      <c r="I109" s="6"/>
     </row>
     <row r="110" spans="1:10" ht="13.5" customHeight="1">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
-      <c r="I110" s="1"/>
+      <c r="I110" s="6"/>
       <c r="J110" s="1"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
-      <c r="I111" s="1"/>
+      <c r="I111" s="6"/>
       <c r="J111" s="1"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1">
       <c r="A112" s="1"/>
-      <c r="I112" s="1"/>
+      <c r="I112" s="6"/>
       <c r="J112" s="1"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1">
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
-      <c r="I113" s="1"/>
+      <c r="I113" s="6"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1">
       <c r="A114" s="1"/>
@@ -2019,17 +1968,17 @@
     <row r="116" spans="1:10" ht="13.5" customHeight="1">
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
-      <c r="I116" s="1"/>
+      <c r="I116" s="6"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1">
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
-      <c r="I117" s="1"/>
+      <c r="I117" s="6"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1">
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
-      <c r="I118" s="1"/>
+      <c r="I118" s="6"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1">
       <c r="A119" s="1"/>
@@ -2038,18 +1987,18 @@
     <row r="120" spans="1:10" ht="13.5" customHeight="1">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
-      <c r="I120" s="1"/>
+      <c r="I120" s="6"/>
       <c r="J120" s="1"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1">
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
-      <c r="I121" s="1"/>
+      <c r="I121" s="6"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
-      <c r="I122" s="1"/>
+      <c r="I122" s="6"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1">
       <c r="A123" s="1"/>
@@ -2059,7 +2008,7 @@
       <c r="A124" s="1"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I125" s="1"/>
+      <c r="I125" s="6"/>
     </row>
     <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="A126" s="1"/>
@@ -2071,33 +2020,33 @@
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
+      <c r="I128" s="6"/>
     </row>
     <row r="129" spans="1:9" ht="13.5" customHeight="1">
       <c r="A129" s="1"/>
       <c r="H129" s="1"/>
-      <c r="I129" s="1"/>
+      <c r="I129" s="6"/>
     </row>
     <row r="130" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I130" s="1"/>
+      <c r="I130" s="6"/>
     </row>
     <row r="131" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I131" s="1"/>
+      <c r="I131" s="6"/>
     </row>
     <row r="132" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I132" s="1"/>
+      <c r="I132" s="6"/>
     </row>
     <row r="133" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I133" s="1"/>
+      <c r="I133" s="6"/>
     </row>
     <row r="134" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I134" s="1"/>
+      <c r="I134" s="6"/>
     </row>
     <row r="135" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I135" s="1"/>
+      <c r="I135" s="6"/>
     </row>
     <row r="136" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I136" s="1"/>
+      <c r="I136" s="6"/>
     </row>
     <row r="137" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="138" spans="1:9" ht="13.5" customHeight="1"/>

--- a/Assets/test260903/chapter0102.xlsx
+++ b/Assets/test260903/chapter0102.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="779" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2243162-63C2-478F-A851-48308EC26EDB}"/>
+  <xr:revisionPtr revIDLastSave="887" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A640F380-C2A0-442C-B01B-26D298745635}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="116">
   <si>
     <t>Command</t>
   </si>
@@ -223,16 +223,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t xml:space="preserve">浪川有希
-</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t xml:space="preserve">通常
-</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>……そうだと思った</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -721,6 +711,352 @@
     </rPh>
     <rPh sb="11" eb="12">
       <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>てっきり有希が一方的に、
+オレをマネージャーと呼んでいるのだと</t>
+    <rPh sb="7" eb="10">
+      <t>イッポウテキ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希には申し訳ないけど忘れてた、
+そんな約束をしていたなんて……えっと……</t>
+    <rPh sb="4" eb="5">
+      <t>モウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ワケ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ワス</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヤクソク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>も、もちろん……！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ごめん、忘れてた</t>
+    <rPh sb="4" eb="5">
+      <t>ワス</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だから……嘘が下手すぎるよ
+顔に忘れたって書いてあるもん</t>
+    <rPh sb="5" eb="6">
+      <t>ウソ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘタ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ワス</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>まぁ、しょうがないけど……
+幼稚園の頃だから……10年くらい前だし</t>
+    <rPh sb="14" eb="17">
+      <t>ヨウチエン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>コロ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-5-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-5-b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-5合流</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ははっ、まったく……仕方ないなぁ</t>
+    <rPh sb="10" eb="12">
+      <t>シカタ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも、これで思い出したよね？</t>
+    <rPh sb="6" eb="7">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>それじゃ、こうしない？
+今ここで、また約束しようよ！</t>
+    <rPh sb="12" eb="13">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヤクソク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>私は役者に、あなたは作家に！
+どっちも自分の夢を叶えるって……！</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヤクシャ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サッカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カナ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そのために、頑張るって！</t>
+    <rPh sb="6" eb="8">
+      <t>ガンバ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希が手を差し出した</t>
+    <rPh sb="3" eb="4">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>今、目の前にある有希の手を振り返したら、
+この「約束」は成立する</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヤクソク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セイリツ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>夢は簡単には叶わない。
+そんなことは重々分かっている</t>
+    <rPh sb="0" eb="1">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンタン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カナ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジュウジュウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>けれど、僕だって……</t>
+    <rPh sb="4" eb="5">
+      <t>ボク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>僕は有希の手を振り返した。
+そして、大きく頷いた</t>
+    <rPh sb="0" eb="1">
+      <t>ボク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ウナズ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>よし……！　お互い頑張ろうね。
+大丈夫、きっと上手くいくよ</t>
+    <rPh sb="7" eb="8">
+      <t>タガ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガンバ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ダイジョウブ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ウマ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>私は誰よりもあなたを知っている。
+だから、断言できるの</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ダンゲン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>絶対、夢を叶えられるってね</t>
+    <rPh sb="0" eb="2">
+      <t>ゼッタイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カナ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0102-6-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希もね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……そう言ってもらえると嬉しいいよ。
+あなたは、私を一番よく知ってる人だから</t>
+    <rPh sb="4" eb="5">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ウレ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ヒト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>期待して待ってて。
+役者になる夢、絶対に叶えてくる！</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヤクシャ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゼッタイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カナ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……ふふ♪　約束したけんね</t>
+    <rPh sb="6" eb="8">
+      <t>ヤクソク</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -786,7 +1122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -816,14 +1152,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1184,22 +1514,22 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="29.4" customHeight="1">
-      <c r="B11" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>46</v>
+      <c r="B11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="25.2" customHeight="1">
-      <c r="B12" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>46</v>
+      <c r="B12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>37</v>
@@ -1207,11 +1537,11 @@
       <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:12" ht="27" customHeight="1">
-      <c r="B13" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>46</v>
+      <c r="B13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>38</v>
@@ -1266,14 +1596,14 @@
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="3"/>
       <c r="I20" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1">
@@ -1290,19 +1620,19 @@
         <v>26</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="1"/>
       <c r="I23" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J23" s="1"/>
     </row>
@@ -1323,7 +1653,7 @@
         <v>26</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="29.4" customHeight="1">
@@ -1334,7 +1664,7 @@
         <v>26</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="28.2" customHeight="1">
@@ -1345,7 +1675,7 @@
         <v>26</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J27" s="1"/>
     </row>
@@ -1357,7 +1687,7 @@
         <v>26</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J28" s="1"/>
     </row>
@@ -1369,7 +1699,7 @@
         <v>26</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="27" customHeight="1">
@@ -1381,7 +1711,7 @@
         <v>26</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="27.6" customHeight="1">
@@ -1392,57 +1722,57 @@
         <v>26</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="I32" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="27" customHeight="1">
       <c r="B33" s="3"/>
       <c r="I33" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="27" customHeight="1">
       <c r="A34" s="3"/>
       <c r="I34" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="27.6" customHeight="1">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="I35" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C36" s="3"/>
       <c r="I36" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C37" s="3"/>
       <c r="I37" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1">
@@ -1471,12 +1801,12 @@
         <v>26</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>32</v>
@@ -1497,7 +1827,7 @@
         <v>26</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="26.4" customHeight="1">
@@ -1508,13 +1838,13 @@
         <v>26</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>32</v>
@@ -1539,7 +1869,7 @@
         <v>26</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J47" s="1"/>
     </row>
@@ -1547,7 +1877,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="I48" s="10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J48" s="1"/>
     </row>
@@ -1556,11 +1886,11 @@
       <c r="B49" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="C49" s="13" t="s">
         <v>25</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J49" s="1"/>
     </row>
@@ -1568,11 +1898,11 @@
       <c r="B50" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="13" t="s">
         <v>25</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="28.8" customHeight="1">
@@ -1583,51 +1913,51 @@
         <v>26</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="28.8" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="13" t="s">
         <v>25</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="27.6" customHeight="1">
       <c r="B53" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="13" t="s">
         <v>25</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1">
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="I54" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="27.6" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="I55" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="27.6" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="I56" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="27.6" customHeight="1">
@@ -1635,14 +1965,14 @@
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="I57" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="27.6" customHeight="1">
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="I58" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="28.2" customHeight="1">
@@ -1653,24 +1983,24 @@
         <v>26</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C60" s="1"/>
       <c r="I60" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="3"/>
@@ -1686,46 +2016,46 @@
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="28.2" customHeight="1">
       <c r="A63" s="1"/>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>26</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B64" s="14" t="s">
+      <c r="B64" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>26</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="27.6" customHeight="1">
       <c r="A65" s="1"/>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>26</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="27" customHeight="1">
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C66" s="12" t="s">
@@ -1733,173 +2063,326 @@
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="27.6" customHeight="1">
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>26</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="28.2" customHeight="1">
       <c r="A68" s="1"/>
-      <c r="B68" s="14" t="s">
-        <v>23</v>
+      <c r="B68" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>26</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1">
       <c r="I69" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="27.6" customHeight="1">
+      <c r="I70" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="27.6" customHeight="1">
+      <c r="I71" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="13.5" customHeight="1"/>
-    <row r="71" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I71" s="6"/>
-    </row>
-    <row r="72" spans="1:10" ht="13.5" customHeight="1"/>
+    <row r="72" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A72" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B73" s="1"/>
+      <c r="A73" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="C73" s="1"/>
-      <c r="I73" s="6"/>
+      <c r="I73" s="6" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A74" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="I75" s="6"/>
+    <row r="75" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B75" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="J75" s="1"/>
     </row>
-    <row r="76" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I76" s="6"/>
+    <row r="76" spans="1:10" ht="27" customHeight="1">
+      <c r="B76" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A77" t="s">
+        <v>17</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="I77" s="6"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A78" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="I78" s="6"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1">
       <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="I79" s="6"/>
+      <c r="B79" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="J79" s="1"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1">
       <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="I80" s="6"/>
+      <c r="B80" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="J80" s="1"/>
     </row>
     <row r="81" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A81" s="1"/>
+      <c r="A81" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="82" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A82" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="I82" s="6"/>
     </row>
-    <row r="83" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="I83" s="6"/>
-    </row>
-    <row r="84" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="I84" s="6"/>
+    <row r="83" spans="1:9" ht="27" customHeight="1">
+      <c r="B83" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B84" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="85" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="I85" s="6"/>
+      <c r="B85" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="86" spans="1:9" ht="13.5" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
-    </row>
-    <row r="87" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I86" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="28.2" customHeight="1">
       <c r="A87" s="1"/>
-    </row>
-    <row r="88" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I87" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="27.6" customHeight="1">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
-      <c r="I88" s="6"/>
+      <c r="I88" s="9" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="89" spans="1:9" ht="13.5" customHeight="1">
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
-      <c r="I89" s="6"/>
-    </row>
-    <row r="90" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I89" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="28.2" customHeight="1">
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
-      <c r="I90" s="6"/>
-    </row>
-    <row r="91" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="I91" s="6"/>
-    </row>
-    <row r="92" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I90" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B91" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="27.6" customHeight="1">
       <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
+      <c r="B92" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I92" s="10" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="93" spans="1:9" ht="13.5" customHeight="1">
       <c r="A93" s="1"/>
+      <c r="I93" s="8" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="94" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I94" s="6"/>
+      <c r="A94" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="95" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A95" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="I95" s="6"/>
     </row>
-    <row r="96" spans="1:9" ht="13.5" customHeight="1">
+    <row r="96" spans="1:9" ht="27.6" customHeight="1">
       <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
-      <c r="I96" s="6"/>
-    </row>
-    <row r="97" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A97" s="1" t="s">
+      <c r="B96" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B97" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H97" s="1"/>
+      <c r="I97" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B98" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A99" s="3"/>
+      <c r="B99" s="12"/>
+      <c r="G99" s="3"/>
+      <c r="I99" s="6"/>
+    </row>
+    <row r="100" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="1"/>
+      <c r="G100" s="3"/>
+      <c r="I100" s="6"/>
+    </row>
+    <row r="101" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A101" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H97" s="1"/>
-      <c r="I97" s="6"/>
-    </row>
-    <row r="98" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="I98" s="6"/>
-    </row>
-    <row r="99" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="I99" s="6"/>
-    </row>
-    <row r="100" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-      <c r="I100" s="6"/>
-    </row>
-    <row r="101" spans="1:10" ht="13.5" customHeight="1">
       <c r="I101" s="6"/>
     </row>
     <row r="102" spans="1:10" ht="13.5" customHeight="1">
@@ -1949,7 +2432,6 @@
       <c r="J111" s="1"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A112" s="1"/>
       <c r="I112" s="6"/>
       <c r="J112" s="1"/>
     </row>

--- a/Assets/test260903/chapter0102.xlsx
+++ b/Assets/test260903/chapter0102.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="887" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A640F380-C2A0-442C-B01B-26D298745635}"/>
+  <xr:revisionPtr revIDLastSave="892" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EE00D1B-0C75-4B7F-9699-5FF5207E4D7B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="117">
   <si>
     <t>Command</t>
   </si>
@@ -1058,6 +1058,10 @@
     <rPh sb="6" eb="8">
       <t>ヤクソク</t>
     </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>CharacterOff</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -2159,8 +2163,8 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A77" t="s">
-        <v>17</v>
+      <c r="A77" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>97</v>
@@ -2364,8 +2368,12 @@
       </c>
     </row>
     <row r="99" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="12"/>
+      <c r="A99" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="G99" s="3"/>
       <c r="I99" s="6"/>
     </row>

--- a/Assets/test260903/chapter0102.xlsx
+++ b/Assets/test260903/chapter0102.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="892" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EE00D1B-0C75-4B7F-9699-5FF5207E4D7B}"/>
+  <xr:revisionPtr revIDLastSave="904" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0975F838-D922-460A-9385-EF477A9512D0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chapter0102" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="118">
   <si>
     <t>Command</t>
   </si>
@@ -284,20 +284,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>なんでか……不安でさ。
-凄く、怖いいんちゃね……</t>
-    <rPh sb="6" eb="8">
-      <t>フアン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>スゴ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>コワ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>有希の気持ちは分かるような気がする</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -346,11 +332,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>こんな機会滅多にない。
-普通は一生に一回もないもん</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>Jump</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -1062,6 +1043,30 @@
   </si>
   <si>
     <t>CharacterOff</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>なんでか……不安でさ。
+凄く、怖いんちゃね……</t>
+    <rPh sb="6" eb="8">
+      <t>フアン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>スゴ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>コワ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こんな機会は滅多にない。
+普通は一生に一回もないもん</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>頑張って、頑張って、頑張って、
+絶対に夢を叶えてくるね</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1378,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1055"/>
+  <dimension ref="A1:L1056"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1726,33 +1731,33 @@
         <v>26</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="I32" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="27" customHeight="1">
       <c r="B33" s="3"/>
       <c r="I33" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="27" customHeight="1">
       <c r="A34" s="3"/>
       <c r="I34" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="27.6" customHeight="1">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="I35" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1">
@@ -1764,7 +1769,7 @@
       </c>
       <c r="C36" s="3"/>
       <c r="I36" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1">
@@ -1776,7 +1781,7 @@
       </c>
       <c r="C37" s="3"/>
       <c r="I37" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1">
@@ -1805,12 +1810,12 @@
         <v>26</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>32</v>
@@ -1831,7 +1836,7 @@
         <v>26</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="26.4" customHeight="1">
@@ -1842,13 +1847,13 @@
         <v>26</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>32</v>
@@ -1873,7 +1878,7 @@
         <v>26</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J47" s="1"/>
     </row>
@@ -1881,7 +1886,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="I48" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J48" s="1"/>
     </row>
@@ -1894,7 +1899,7 @@
         <v>25</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J49" s="1"/>
     </row>
@@ -1906,7 +1911,7 @@
         <v>25</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="28.8" customHeight="1">
@@ -1917,7 +1922,7 @@
         <v>26</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="28.8" customHeight="1">
@@ -1929,113 +1934,114 @@
         <v>25</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="27.6" customHeight="1">
-      <c r="B53" s="12" t="s">
-        <v>24</v>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A53" s="1"/>
+      <c r="B53" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>25</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="I54" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="I55" s="9" t="s">
-        <v>74</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B54" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="I55" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="27.6" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="I56" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A57" s="3"/>
+      <c r="A57" s="1"/>
       <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
       <c r="I57" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A58" s="3"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="I58" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="I59" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B60" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A61" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B59" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I59" s="9" t="s">
+      <c r="C61" s="1"/>
+      <c r="I61" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A60" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B60" s="1" t="s">
+    <row r="62" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A62" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62" s="1"/>
+      <c r="C62" s="3"/>
+      <c r="I62" s="6"/>
+    </row>
+    <row r="63" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H63" s="1"/>
+      <c r="I63" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C60" s="1"/>
-      <c r="I60" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A61" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B61" s="1"/>
-      <c r="C61" s="3"/>
-      <c r="I61" s="6"/>
-    </row>
-    <row r="62" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="1"/>
-      <c r="I62" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A63" s="1"/>
-      <c r="B63" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I63" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="28.8" customHeight="1">
+    </row>
+    <row r="64" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A64" s="1"/>
       <c r="B64" s="13" t="s">
         <v>23</v>
       </c>
@@ -2043,11 +2049,10 @@
         <v>26</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A65" s="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="28.8" customHeight="1">
       <c r="B65" s="13" t="s">
         <v>23</v>
       </c>
@@ -2055,103 +2060,103 @@
         <v>26</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="27" customHeight="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A66" s="1"/>
       <c r="B66" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="H66" s="1"/>
       <c r="I66" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="27.6" customHeight="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="27" customHeight="1">
       <c r="B67" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>26</v>
       </c>
+      <c r="H67" s="1"/>
       <c r="I67" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B68" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A69" s="1"/>
+      <c r="B69" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I70" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A68" s="1"/>
-      <c r="B68" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I68" s="10" t="s">
+    <row r="71" spans="1:10" ht="27.6" customHeight="1">
+      <c r="I71" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I69" s="6" t="s">
+    <row r="72" spans="1:10" ht="27.6" customHeight="1">
+      <c r="I72" s="9" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="27.6" customHeight="1">
-      <c r="I70" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="27.6" customHeight="1">
-      <c r="I71" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A72" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I72" s="8" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1">
       <c r="A73" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="I73" s="6" t="s">
-        <v>92</v>
+      <c r="B73" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B74" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="C74" s="1"/>
-      <c r="I74" s="6"/>
-    </row>
-    <row r="75" spans="1:10" ht="27.6" customHeight="1">
-      <c r="B75" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I75" s="9" t="s">
+      <c r="I74" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A75" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="J75" s="1"/>
-    </row>
-    <row r="76" spans="1:10" ht="27" customHeight="1">
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="I75" s="6"/>
+    </row>
+    <row r="76" spans="1:10" ht="27.6" customHeight="1">
       <c r="B76" s="12" t="s">
         <v>24</v>
       </c>
@@ -2159,36 +2164,35 @@
         <v>26</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A77" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I77" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:10" ht="27" customHeight="1">
+      <c r="B77" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>96</v>
+        <v>61</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="I78" s="6"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A79" s="1"/>
-      <c r="B79" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I79" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="J79" s="1"/>
+      <c r="A79" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I79" s="6"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1">
       <c r="A80" s="1"/>
@@ -2199,201 +2203,211 @@
         <v>26</v>
       </c>
       <c r="I80" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J80" s="1"/>
+    </row>
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A81" s="1"/>
+      <c r="B81" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J81" s="1"/>
+    </row>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A82" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A83" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="I83" s="6"/>
+    </row>
+    <row r="84" spans="1:10" ht="27" customHeight="1">
+      <c r="B84" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B85" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I85" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="J80" s="1"/>
-    </row>
-    <row r="81" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A81" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A82" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="I82" s="6"/>
-    </row>
-    <row r="83" spans="1:9" ht="27" customHeight="1">
-      <c r="B83" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I83" s="9" t="s">
+    </row>
+    <row r="86" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B86" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I86" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="27.6" customHeight="1">
-      <c r="B84" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C84" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I84" s="9" t="s">
+    <row r="87" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="I87" s="8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B85" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I85" s="6" t="s">
+    <row r="88" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A88" s="1"/>
+      <c r="I88" s="10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="I86" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="28.2" customHeight="1">
-      <c r="A87" s="1"/>
-      <c r="I87" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="27.6" customHeight="1">
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="I88" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="13.5" customHeight="1">
+    <row r="89" spans="1:10" ht="27.6" customHeight="1">
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
-      <c r="I89" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="28.2" customHeight="1">
+      <c r="I89" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="13.5" customHeight="1">
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
-      <c r="I90" s="9" t="s">
+      <c r="I90" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="I91" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B92" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A93" s="1"/>
+      <c r="B93" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I93" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B91" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C91" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I91" s="9" t="s">
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A94" s="1"/>
+      <c r="I94" s="8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="27.6" customHeight="1">
-      <c r="A92" s="1"/>
-      <c r="B92" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C92" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I92" s="10" t="s">
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A95" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A93" s="1"/>
-      <c r="I93" s="8" t="s">
+      <c r="I95" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A94" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B94" s="3" t="s">
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A96" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I96" s="6"/>
+    </row>
+    <row r="97" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A97" s="1"/>
+      <c r="B97" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I97" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="I94" s="6" t="s">
+    </row>
+    <row r="98" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B98" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H98" s="1"/>
+      <c r="I98" s="9" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A95" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="I95" s="6"/>
-    </row>
-    <row r="96" spans="1:9" ht="27.6" customHeight="1">
-      <c r="A96" s="1"/>
-      <c r="B96" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I96" s="9" t="s">
+    <row r="99" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B99" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I99" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B97" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C97" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="1"/>
-      <c r="I97" s="9" t="s">
+    <row r="100" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A100" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B98" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C98" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A99" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B99" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G99" s="3"/>
-      <c r="I99" s="6"/>
-    </row>
-    <row r="100" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="1"/>
+      <c r="B100" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="G100" s="3"/>
       <c r="I100" s="6"/>
     </row>
     <row r="101" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="1"/>
+      <c r="G101" s="3"/>
+      <c r="I101" s="6"/>
+    </row>
+    <row r="102" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A102" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I101" s="6"/>
-    </row>
-    <row r="102" spans="1:10" ht="13.5" customHeight="1">
       <c r="I102" s="6"/>
     </row>
     <row r="103" spans="1:10" ht="13.5" customHeight="1">
@@ -2403,8 +2417,6 @@
       <c r="I104" s="6"/>
     </row>
     <row r="105" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
       <c r="I105" s="6"/>
     </row>
     <row r="106" spans="1:10" ht="13.5" customHeight="1">
@@ -2428,10 +2440,9 @@
       <c r="I109" s="6"/>
     </row>
     <row r="110" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A110" s="1"/>
       <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
       <c r="I110" s="6"/>
-      <c r="J110" s="1"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1">
       <c r="A111" s="1"/>
@@ -2440,25 +2451,26 @@
       <c r="J111" s="1"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
       <c r="I112" s="6"/>
       <c r="J112" s="1"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
       <c r="I113" s="6"/>
+      <c r="J113" s="1"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A114" s="1"/>
       <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="I114" s="6"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1">
       <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="I116" s="6"/>
+      <c r="A116" s="1"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1">
       <c r="B117" s="1"/>
@@ -2471,19 +2483,19 @@
       <c r="I118" s="6"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A119" s="1"/>
       <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="I119" s="6"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="1"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A121" s="1"/>
       <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
       <c r="I121" s="6"/>
+      <c r="J121" s="1"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="B122" s="1"/>
@@ -2491,33 +2503,35 @@
       <c r="I122" s="6"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A123" s="1"/>
       <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="I123" s="6"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1">
       <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I125" s="6"/>
+      <c r="A125" s="1"/>
     </row>
     <row r="126" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A126" s="1"/>
+      <c r="I126" s="6"/>
     </row>
     <row r="127" spans="1:10" ht="13.5" customHeight="1">
       <c r="A127" s="1"/>
     </row>
     <row r="128" spans="1:10" ht="13.5" customHeight="1">
       <c r="A128" s="1"/>
-      <c r="B128" s="1"/>
-      <c r="H128" s="1"/>
-      <c r="I128" s="6"/>
     </row>
     <row r="129" spans="1:9" ht="13.5" customHeight="1">
       <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
       <c r="H129" s="1"/>
       <c r="I129" s="6"/>
     </row>
     <row r="130" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A130" s="1"/>
+      <c r="H130" s="1"/>
       <c r="I130" s="6"/>
     </row>
     <row r="131" spans="1:9" ht="13.5" customHeight="1">
@@ -2538,7 +2552,9 @@
     <row r="136" spans="1:9" ht="13.5" customHeight="1">
       <c r="I136" s="6"/>
     </row>
-    <row r="137" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="137" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I137" s="6"/>
+    </row>
     <row r="138" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="139" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="140" spans="1:9" ht="13.5" customHeight="1"/>
@@ -3457,6 +3473,7 @@
     <row r="1053" ht="13.5" customHeight="1"/>
     <row r="1054" ht="13.5" customHeight="1"/>
     <row r="1055" ht="13.5" customHeight="1"/>
+    <row r="1056" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0102.xlsx
+++ b/Assets/test260903/chapter0102.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="904" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0975F838-D922-460A-9385-EF477A9512D0}"/>
+  <xr:revisionPtr revIDLastSave="910" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1ED150E-3967-4D81-AC53-4C8A8A3E5C87}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -624,23 +624,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>そしたらあなたが本が、
-映画やドラマになったら私が演じるって</t>
-    <rPh sb="8" eb="9">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>エイガ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>エン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>で、そうなった時は自分のことを
 センセーと呼んでくれって</t>
     <rPh sb="7" eb="8">
@@ -672,20 +655,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>そう言う約束だったんだけど、
-まさか忘れたの？</t>
-    <rPh sb="2" eb="3">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヤクソク</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ワス</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>えっ、僕……そんなこと言ったの？</t>
     <rPh sb="3" eb="4">
       <t>ボク</t>
@@ -707,23 +676,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>有希には申し訳ないけど忘れてた、
-そんな約束をしていたなんて……えっと……</t>
-    <rPh sb="4" eb="5">
-      <t>モウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ワケ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ワス</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ヤクソク</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>も、もちろん……！</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -731,26 +683,6 @@
     <t>ごめん、忘れてた</t>
     <rPh sb="4" eb="5">
       <t>ワス</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>だから……嘘が下手すぎるよ
-顔に忘れたって書いてあるもん</t>
-    <rPh sb="5" eb="6">
-      <t>ウソ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ヘタ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>カオ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ワス</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>カ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -911,29 +843,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>僕は有希の手を振り返した。
-そして、大きく頷いた</t>
-    <rPh sb="0" eb="1">
-      <t>ボク</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>テ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>カエ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ウナズ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>よし……！　お互い頑張ろうね。
 大丈夫、きっと上手くいくよ</t>
     <rPh sb="7" eb="8">
@@ -968,19 +877,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>絶対、夢を叶えられるってね</t>
-    <rPh sb="0" eb="2">
-      <t>ゼッタイ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ユメ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>カナ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>*選択肢0102-6-a</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -1067,6 +963,107 @@
   <si>
     <t>頑張って、頑張って、頑張って、
 絶対に夢を叶えてくるね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そしてあなたの本が、
+映画やドラマになったら私が演じるって</t>
+    <rPh sb="7" eb="8">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>エイガ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そう言う約束だったんだけど、
+まさか忘れてたの？</t>
+    <rPh sb="2" eb="3">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヤクソク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ワス</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有希には申し訳ないけど忘れてた、
+そんな約束をしてたなんて……えっと……</t>
+    <rPh sb="4" eb="5">
+      <t>モウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ワケ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ワス</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヤクソク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だから……嘘が下手すぎるよ
+顔に忘れてたって書いてあるもん</t>
+    <rPh sb="5" eb="6">
+      <t>ウソ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘタ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ワス</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>僕は有希の手を握り返した。
+そして、大きく頷いた</t>
+    <rPh sb="0" eb="1">
+      <t>ボク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ウナズ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>絶対、夢を叶えられるって</t>
+    <rPh sb="0" eb="2">
+      <t>ゼッタイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カナ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1731,7 +1728,7 @@
         <v>26</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1">
@@ -1810,7 +1807,7 @@
         <v>26</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1">
@@ -1946,7 +1943,7 @@
         <v>25</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="27.6" customHeight="1">
@@ -2072,7 +2069,7 @@
         <v>26</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="27" customHeight="1">
@@ -2084,7 +2081,7 @@
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="27.6" customHeight="1">
@@ -2095,7 +2092,7 @@
         <v>26</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="28.2" customHeight="1">
@@ -2107,22 +2104,22 @@
         <v>26</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1">
       <c r="I70" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="27.6" customHeight="1">
       <c r="I71" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="27.6" customHeight="1">
       <c r="I72" s="9" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1">
@@ -2130,10 +2127,10 @@
         <v>46</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1">
@@ -2141,16 +2138,16 @@
         <v>46</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C74" s="1"/>
       <c r="I74" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2164,7 +2161,7 @@
         <v>26</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="J76" s="1"/>
     </row>
@@ -2176,7 +2173,7 @@
         <v>26</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1">
@@ -2184,13 +2181,13 @@
         <v>61</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I78" s="6"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I79" s="6"/>
     </row>
@@ -2203,7 +2200,7 @@
         <v>26</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J80" s="1"/>
     </row>
@@ -2216,7 +2213,7 @@
         <v>26</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="J81" s="1"/>
     </row>
@@ -2225,12 +2222,12 @@
         <v>61</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2244,7 +2241,7 @@
         <v>26</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="27.6" customHeight="1">
@@ -2255,7 +2252,7 @@
         <v>26</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1">
@@ -2266,41 +2263,41 @@
         <v>26</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="I87" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="28.2" customHeight="1">
       <c r="A88" s="1"/>
       <c r="I88" s="10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="27.6" customHeight="1">
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="I89" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1">
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="I90" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="28.2" customHeight="1">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="I91" s="9" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="28.8" customHeight="1">
@@ -2311,7 +2308,7 @@
         <v>26</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="27.6" customHeight="1">
@@ -2323,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1">
       <c r="A94" s="1"/>
       <c r="I94" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1">
@@ -2337,15 +2334,15 @@
         <v>46</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I96" s="6"/>
     </row>
@@ -2358,7 +2355,7 @@
         <v>26</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="28.8" customHeight="1">
@@ -2370,7 +2367,7 @@
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="13.5" customHeight="1">
@@ -2381,12 +2378,12 @@
         <v>26</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="13.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B100" s="12" t="s">
         <v>24</v>

--- a/Assets/test260903/chapter0102.xlsx
+++ b/Assets/test260903/chapter0102.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="910" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1ED150E-3967-4D81-AC53-4C8A8A3E5C87}"/>
+  <xr:revisionPtr revIDLastSave="959" documentId="11_9F6694A0EEBACB1C9082A027A8BF20B2877551EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A4A1BDB-3968-4677-9FA7-2873B4A3C2DA}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="123">
   <si>
     <t>Command</t>
   </si>
@@ -1065,6 +1065,23 @@
       <t>カナ</t>
     </rPh>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>悲しみ</t>
+  </si>
+  <si>
+    <t>悲しみ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>喜び</t>
+  </si>
+  <si>
+    <t>喜び</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>怒り</t>
   </si>
 </sst>
 </file>
@@ -1623,7 +1640,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>47</v>
@@ -1725,7 +1742,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="I31" s="9" t="s">
         <v>109</v>
@@ -1804,7 +1821,7 @@
         <v>24</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="I40" s="10" t="s">
         <v>110</v>
@@ -1830,7 +1847,7 @@
         <v>24</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="I43" s="10" t="s">
         <v>62</v>
@@ -1841,7 +1858,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="I44" s="10" t="s">
         <v>63</v>
@@ -1871,8 +1888,8 @@
       <c r="B47" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C47" s="11" t="s">
-        <v>26</v>
+      <c r="C47" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="I47" s="10" t="s">
         <v>64</v>
@@ -1915,8 +1932,8 @@
       <c r="B51" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C51" s="11" t="s">
-        <v>26</v>
+      <c r="C51" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="I51" s="9" t="s">
         <v>68</v>
@@ -1927,8 +1944,8 @@
       <c r="B52" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>25</v>
+      <c r="C52" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="I52" s="9" t="s">
         <v>69</v>
@@ -1939,8 +1956,8 @@
       <c r="B53" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C53" s="13" t="s">
-        <v>25</v>
+      <c r="C53" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="I53" s="9" t="s">
         <v>111</v>
@@ -1950,8 +1967,8 @@
       <c r="B54" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>25</v>
+      <c r="C54" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>70</v>
@@ -2030,7 +2047,7 @@
         <v>24</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="6" t="s">
@@ -2101,7 +2118,7 @@
         <v>24</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="I69" s="10" t="s">
         <v>113</v>
@@ -2158,7 +2175,7 @@
         <v>24</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="I76" s="9" t="s">
         <v>115</v>
@@ -2170,7 +2187,7 @@
         <v>24</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="I77" s="9" t="s">
         <v>88</v>
@@ -2196,8 +2213,8 @@
       <c r="B80" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C80" s="12" t="s">
-        <v>26</v>
+      <c r="C80" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>92</v>
@@ -2238,7 +2255,7 @@
         <v>24</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I84" s="9" t="s">
         <v>94</v>
@@ -2249,7 +2266,7 @@
         <v>24</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="I85" s="9" t="s">
         <v>95</v>
@@ -2259,8 +2276,8 @@
       <c r="B86" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C86" s="12" t="s">
-        <v>26</v>
+      <c r="C86" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>96</v>
@@ -2305,7 +2322,7 @@
         <v>24</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="I92" s="9" t="s">
         <v>101</v>
@@ -2325,6 +2342,12 @@
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1">
       <c r="A94" s="1"/>
+      <c r="B94" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="I94" s="8" t="s">
         <v>117</v>
       </c>
@@ -2352,7 +2375,7 @@
         <v>24</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="I97" s="9" t="s">
         <v>105</v>
@@ -2363,7 +2386,7 @@
         <v>24</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="9" t="s">
@@ -2374,8 +2397,8 @@
       <c r="B99" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C99" s="12" t="s">
-        <v>26</v>
+      <c r="C99" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="I99" s="6" t="s">
         <v>107</v>
